--- a/reports/pdf_rolling5_20260903.xlsx
+++ b/reports/pdf_rolling5_20260903.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,489억   ·   현금 66억(1.5%)      오늘 2026-09-03  vs  5일전 2026-08-27      매수 11종목  /  매도 11종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,425억   ·   현금 33억(0.7%)      오늘 2026-09-03  vs  5일전 2026-08-27      매수 11종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>109</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1346286250</v>
+        <v>1343659350</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-98</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-6468980000</v>
+        <v>-6456357600</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>41</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>2118060000</v>
+        <v>2113927200</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-32</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2381280000</v>
+        <v>-2376633600</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>36</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>2605140000</v>
+        <v>2600056800</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-29</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1504085000</v>
+        <v>-1501150200</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>29</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>2437450000</v>
+        <v>2432694000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-28</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1633030000</v>
+        <v>-1629843600</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>23</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>795656250</v>
+        <v>794103750</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-20</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-848700000</v>
+        <v>-847044000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2250900000</v>
+        <v>2246508000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-10</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1037300000</v>
+        <v>-1035276000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>18</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>876375000</v>
+        <v>874665000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-8</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-2025400000</v>
+        <v>-2021448000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>4944600000</v>
+        <v>4934952000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-7</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-351933750</v>
+        <v>-351247050</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>9</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>447412500</v>
+        <v>446539500</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1036,23 +1036,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-2011562500</v>
+        <v>-354469500</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>2.90%→2.19%</t>
+          <t>1.21%→1.08%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>29→24</t>
+          <t>72→67</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
         <v>5</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>873812500</v>
+        <v>872107500</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1080,23 +1080,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-355162500</v>
+        <v>-2007637500</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>1.21%→1.08%</t>
+          <t>2.90%→2.19%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>72→67</t>
+          <t>29→24</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>719550000</v>
+        <v>718146000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>-4</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-372280000</v>
+        <v>-371553600</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,768억   ·   현금 24억(0.7%)      오늘 2026-09-03  vs  5일전 2026-08-27      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,652억   ·   현금 12억(0.3%)      오늘 2026-09-03  vs  5일전 2026-08-27      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1171,7 +1171,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,513억   ·   현금 72억(2.9%)      오늘 2026-09-03  vs  5일전 2026-08-27      매수 7종목  /  매도 5종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,471억   ·   현금 36억(1.5%)      오늘 2026-09-03  vs  5일전 2026-08-27      매수 7종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1267,7 +1267,7 @@
         <v>334</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2407204800</v>
+        <v>2403731200</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>-92</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-1370754000</v>
+        <v>-1368776000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>98</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>3422865600</v>
+        <v>3417926400</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>-37</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-6423070500</v>
+        <v>-6413802000</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>1363824000</v>
+        <v>1361856000</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>-29</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-2055923100</v>
+        <v>-2052956400</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>19</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>1319333400</v>
+        <v>1317429600</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>-15</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1282743000</v>
+        <v>-1280892000</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>14</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>507414600</v>
+        <v>506682400</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>-13</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-1225224000</v>
+        <v>-1223456000</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>8</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>2228688000</v>
+        <v>2225472000</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>4</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>294663600</v>
+        <v>294238400</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,141억   ·   현금 54억(2.5%)      오늘 2026-09-03  vs  5일전 2026-08-27      매수 4종목  /  매도 6종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,065억   ·   현금 27억(1.3%)      오늘 2026-09-03  vs  5일전 2026-08-27      매수 4종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1857,7 +1857,7 @@
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 267억   ·   현금 3억(0.9%)      오늘 2026-09-03  vs  5일전 2026-08-27      매수 13종목  /  매도 9종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 262억   ·   현금 1억(0.5%)      오늘 2026-09-03  vs  5일전 2026-08-27      매수 13종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B42" s="4" t="n"/>
@@ -1953,11 +1953,11 @@
         <v>89</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>128800800</v>
+        <v>120301300</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>2.08%→2.55%</t>
+          <t>2.04%→2.50%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -1974,11 +1974,11 @@
         <v>-344</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-271457280</v>
+        <v>-250432000</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>8.82%→7.81%</t>
+          <t>8.55%→7.56%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
@@ -1997,11 +1997,11 @@
         <v>53</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>140428800</v>
+        <v>123914000</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>7.03%→7.53%</t>
+          <t>6.52%→6.97%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -2018,11 +2018,11 @@
         <v>-90</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-84758400</v>
+        <v>-77994000</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>2.96%→2.64%</t>
+          <t>2.86%→2.55%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
@@ -2041,11 +2041,11 @@
         <v>45</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>103356000</v>
+        <v>106470000</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>2.77%→3.14%</t>
+          <t>3.00%→3.40%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -2062,11 +2062,11 @@
         <v>-71</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-52602480</v>
+        <v>-49501200</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>1.27%→1.08%</t>
+          <t>1.26%→1.06%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -2085,11 +2085,11 @@
         <v>31</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>19239840</v>
+        <v>18770500</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>0.43%→0.50%</t>
+          <t>0.45%→0.52%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2106,11 +2106,11 @@
         <v>-44</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-128462400</v>
+        <v>-121968000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>3.21%→2.73%</t>
+          <t>3.20%→2.72%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -2129,11 +2129,11 @@
         <v>30</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>55188000</v>
+        <v>55335000</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>2.23%→2.43%</t>
+          <t>2.35%→2.55%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2150,11 +2150,11 @@
         <v>-27</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-117806400</v>
+        <v>-111321000</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>2.24%→1.80%</t>
+          <t>2.22%→1.79%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
@@ -2173,11 +2173,11 @@
         <v>29</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>105444000</v>
+        <v>101703000</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>0.63%→1.01%</t>
+          <t>0.63%→1.02%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2194,11 +2194,11 @@
         <v>-19</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-28728000</v>
+        <v>-27597500</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>5.50%→5.38%</t>
+          <t>5.55%→5.43%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
@@ -2217,11 +2217,11 @@
         <v>27</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>105170400</v>
+        <v>105462000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>2.74%→3.12%</t>
+          <t>2.89%→3.28%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -2238,7 +2238,7 @@
         <v>-15</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-35478000</v>
+        <v>-33915000</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>15</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>37098000</v>
+        <v>35385000</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
@@ -2282,11 +2282,11 @@
         <v>-10</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-36720000</v>
+        <v>-35280000</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>1.41%→1.28%</t>
+          <t>1.43%→1.29%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
@@ -2305,11 +2305,11 @@
         <v>11</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>25819200</v>
+        <v>24486000</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>2.16%→2.25%</t>
+          <t>2.15%→2.24%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -2326,11 +2326,11 @@
         <v>-3</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-7549200</v>
+        <v>-7423500</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>0.61%→0.58%</t>
+          <t>0.63%→0.60%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2349,11 +2349,11 @@
         <v>9</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>14385600</v>
+        <v>13167000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>1.66%→1.71%</t>
+          <t>1.60%→1.64%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -2377,7 +2377,7 @@
         <v>8</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>29894400</v>
+        <v>28504000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
@@ -2405,11 +2405,11 @@
         <v>7</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>31802400</v>
+        <v>30772000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>0.98%→1.10%</t>
+          <t>1.00%→1.11%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -2433,11 +2433,11 @@
         <v>3</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>35856000</v>
+        <v>35595000</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>0.09%→0.22%</t>
+          <t>0.09%→0.23%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2454,7 +2454,7 @@
     <row r="59" ht="19" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 535억   ·   현금 8억(1.5%)      오늘 2026-09-03  vs  5일전 2026-08-27      매수 4종목  /  매도 2종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 523억   ·   현금 4억(0.8%)      오늘 2026-09-03  vs  5일전 2026-08-27      매수 4종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B59" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260903.xlsx
+++ b/reports/pdf_rolling5_20260903.xlsx
@@ -1036,23 +1036,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-354469500</v>
+        <v>-2007637500</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>1.21%→1.08%</t>
+          <t>2.90%→2.19%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>72→67</t>
+          <t>29→24</t>
         </is>
       </c>
     </row>
@@ -1080,23 +1080,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-2007637500</v>
+        <v>-354469500</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>2.90%→2.19%</t>
+          <t>1.21%→1.08%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>29→24</t>
+          <t>72→67</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260903.xlsx
+++ b/reports/pdf_rolling5_20260903.xlsx
@@ -1036,23 +1036,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-2007637500</v>
+        <v>-354469500</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>2.90%→2.19%</t>
+          <t>1.21%→1.08%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>29→24</t>
+          <t>72→67</t>
         </is>
       </c>
     </row>
@@ -1080,23 +1080,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-354469500</v>
+        <v>-2007637500</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>1.21%→1.08%</t>
+          <t>2.90%→2.19%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>72→67</t>
+          <t>29→24</t>
         </is>
       </c>
     </row>
